--- a/Result/profitability/8481.xlsx
+++ b/Result/profitability/8481.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM47"/>
+  <dimension ref="A1:AM48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6399,6 +6399,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>8481</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>306</v>
+      </c>
+      <c r="D48" t="n">
+        <v>168</v>
+      </c>
+      <c r="E48" t="n">
+        <v>138</v>
+      </c>
+      <c r="F48" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="G48" t="n">
+        <v>58</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>18.84%</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>62</v>
+      </c>
+      <c r="K48" t="n">
+        <v>54</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="N48" t="n">
+        <v>46.9875</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.04999999999999993</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.06493506493506485</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>-1.890000000000001</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-0.04021276595744683</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.7083333333333333</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>-1.539999999999999</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>-0.03301178992497322</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK48" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
